--- a/ZonasEscolares/excels/TACNA-TACNA-TACNA.xlsx
+++ b/ZonasEscolares/excels/TACNA-TACNA-TACNA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/TACNA-TACNA-TACNA.xlsx
+++ b/ZonasEscolares/excels/TACNA-TACNA-TACNA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>INTERNACIONAL ELIM</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-18.00742</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-70.24200999999999</v>
-      </c>
-      <c r="I2" t="n">
-        <v>209</v>
-      </c>
-      <c r="J2" t="n">
-        <v>21</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-18.00742</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-70.24201</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>WILLIAM PRESCOTT</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-18.02175</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-70.26869000000001</v>
-      </c>
-      <c r="I3" t="n">
-        <v>501</v>
-      </c>
-      <c r="J3" t="n">
-        <v>19</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-18.02175</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-70.26869</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>225 NIÑOS HEROES</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-18.00218</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-70.23723</v>
-      </c>
-      <c r="I4" t="n">
-        <v>328</v>
-      </c>
-      <c r="J4" t="n">
-        <v>16</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-18.00218</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-70.23723</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>CLARITA GAMBETTA</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-18.0292</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-70.26772</v>
-      </c>
-      <c r="I5" t="n">
-        <v>220</v>
-      </c>
-      <c r="J5" t="n">
-        <v>15</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-18.0292</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-70.26772</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>42217 NUESTROS HEROES DE LA GUERRA DEL PACIFICO</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-18.0081</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-70.25818</v>
-      </c>
-      <c r="I6" t="n">
-        <v>994</v>
-      </c>
-      <c r="J6" t="n">
-        <v>46</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-18.0081</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-70.25818</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>994</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>42002 CARLOS WIESSE</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-18.01071</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-70.25084</v>
-      </c>
-      <c r="I7" t="n">
-        <v>474</v>
-      </c>
-      <c r="J7" t="n">
-        <v>21</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-18.01071</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-70.25084</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>42005 JOSE ROSA ARA</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-18.00307</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-70.23729</v>
-      </c>
-      <c r="I8" t="n">
-        <v>665</v>
-      </c>
-      <c r="J8" t="n">
-        <v>35</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-18.00307</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-70.23729</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>42007 LEONCIO PRADO</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-18.00261</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-70.24893</v>
-      </c>
-      <c r="I9" t="n">
-        <v>536</v>
-      </c>
-      <c r="J9" t="n">
-        <v>26</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-18.00261</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-70.24893</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>42011 REPUBLICA ARGENTINA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-18.01512</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-70.25301</v>
-      </c>
-      <c r="I10" t="n">
-        <v>504</v>
-      </c>
-      <c r="J10" t="n">
-        <v>23</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-18.01512</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-70.25301</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>42013 ROSA DOMINGA PEREZ LIENDO</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-18.01292</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-70.2353</v>
-      </c>
-      <c r="I11" t="n">
-        <v>215</v>
-      </c>
-      <c r="J11" t="n">
-        <v>14</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-18.01292</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-70.2353</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>42014 JOSE JIMENEZ BORJA</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-18.00299</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-70.24482</v>
-      </c>
-      <c r="I12" t="n">
-        <v>412</v>
-      </c>
-      <c r="J12" t="n">
-        <v>18</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-18.00299</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-70.24482</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>42015 ZOILA SABEL CACERES</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-18.00042</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-70.24842</v>
-      </c>
-      <c r="I13" t="n">
-        <v>248</v>
-      </c>
-      <c r="J13" t="n">
-        <v>14</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-18.00042</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-70.24842</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>42016 MAXIMILIANA VELASQUEZ DE SOTILLO</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-18.00464</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-70.25445000000001</v>
-      </c>
-      <c r="I14" t="n">
-        <v>309</v>
-      </c>
-      <c r="J14" t="n">
-        <v>17</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-18.00464</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-70.25445</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>42020 ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-17.99802</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-70.23855</v>
-      </c>
-      <c r="I15" t="n">
-        <v>229</v>
-      </c>
-      <c r="J15" t="n">
-        <v>15</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-17.99802</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-70.23855</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>42022 DR. MODESTO MONTESINOS ZAMALLOA</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-18.01956</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-70.23916</v>
-      </c>
-      <c r="I16" t="n">
-        <v>273</v>
-      </c>
-      <c r="J16" t="n">
-        <v>21</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-18.01956</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-70.23916</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>COLEGIO DE ALTO RENDIMIENTO DE TACNA</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-18.049298</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-70.283728</v>
-      </c>
-      <c r="I17" t="n">
-        <v>294</v>
-      </c>
-      <c r="J17" t="n">
-        <v>35</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-18.049298</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-70.283728</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>42241 HERMOGENES ARENAS YAÑEZ</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-18.03821</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-70.28108</v>
-      </c>
-      <c r="I18" t="n">
-        <v>611</v>
-      </c>
-      <c r="J18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-18.03821</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-70.28108</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>611</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>MIGUEL PRO</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-18.0678</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-70.29362999999999</v>
-      </c>
-      <c r="I19" t="n">
-        <v>438</v>
-      </c>
-      <c r="J19" t="n">
-        <v>29</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-18.0678</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-70.29363</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>43001 HERMANOS BARRETO</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-18.00799</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-70.24263000000001</v>
-      </c>
-      <c r="I20" t="n">
-        <v>558</v>
-      </c>
-      <c r="J20" t="n">
-        <v>26</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-18.00799</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-70.24263</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>43005 MODESTO MOLINA</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-18.01515</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-70.23356</v>
-      </c>
-      <c r="I21" t="n">
-        <v>225</v>
-      </c>
-      <c r="J21" t="n">
-        <v>16</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-18.01515</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-70.23356</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>43007 LUIS BANCHERO ROSSI</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-17.99919</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-70.23435000000001</v>
-      </c>
-      <c r="I22" t="n">
-        <v>270</v>
-      </c>
-      <c r="J22" t="n">
-        <v>15</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-17.99919</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-70.23435</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>43008 JORGE MARTORELL FLORES</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-18.01189</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-70.24473</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1135</v>
-      </c>
-      <c r="J23" t="n">
-        <v>59</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-18.01189</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-70.24473</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1135</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>43009 MARIA UGARTECHE DE MACLEAN</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-18.00898</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-70.24509999999999</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1170</v>
-      </c>
-      <c r="J24" t="n">
-        <v>62</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-18.00898</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-70.2451</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1170</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>42019 LASTENIA REJAS DE CASTAÑON</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-18.02572</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-70.26607</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1085</v>
-      </c>
-      <c r="J25" t="n">
-        <v>57</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-18.02572</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-70.26607</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>42003 CORONEL GREGORIO ALBARRACIN</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-18.01802</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-70.25331</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1204</v>
-      </c>
-      <c r="J26" t="n">
-        <v>66</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-18.01802</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-70.25331</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1204</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>42010 SANTISIMA NIÑA MARIA</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-18.00584</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-70.23817</v>
-      </c>
-      <c r="I27" t="n">
-        <v>903</v>
-      </c>
-      <c r="J27" t="n">
-        <v>57</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-18.00584</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-70.23817</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>903</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>42195 WILMA SOTILLO DE BACIGALUPO</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-18.03162</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-70.2752</v>
-      </c>
-      <c r="I28" t="n">
-        <v>678</v>
-      </c>
-      <c r="J28" t="n">
-        <v>34</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-18.03162</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-70.2752</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>43003 CARLOS ARMANDO LAURA</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-18.00307</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-70.24244</v>
-      </c>
-      <c r="I29" t="n">
-        <v>855</v>
-      </c>
-      <c r="J29" t="n">
-        <v>47</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-18.00307</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-70.24244</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>855</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>43006 MERCEDES INDACOCHEA</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-18.01151</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-70.25207</v>
-      </c>
-      <c r="I30" t="n">
-        <v>788</v>
-      </c>
-      <c r="J30" t="n">
-        <v>49</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-18.01151</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-70.25207</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>788</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>CORONEL BOLOGNESI</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-18.00538</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-70.25069000000001</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1952</v>
-      </c>
-      <c r="J31" t="n">
-        <v>112</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-18.00538</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-70.25069</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1952</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>FRANCISCO ANTONIO DE ZELA</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-18.00527</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-70.23971</v>
-      </c>
-      <c r="I32" t="n">
-        <v>2267</v>
-      </c>
-      <c r="J32" t="n">
-        <v>136</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-18.00527</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-70.23971</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2267</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>MODESTO BASADRE</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-18.00513</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-70.25673999999999</v>
-      </c>
-      <c r="I33" t="n">
-        <v>905</v>
-      </c>
-      <c r="J33" t="n">
-        <v>76</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-18.00513</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-70.25674</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>905</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>SANTA ANA</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-18.01889</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-70.24963</v>
-      </c>
-      <c r="I34" t="n">
-        <v>610</v>
-      </c>
-      <c r="J34" t="n">
-        <v>72</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-18.01889</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-70.24963</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>CRISTO REY</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-18.03041</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-70.27101</v>
-      </c>
-      <c r="I35" t="n">
-        <v>961</v>
-      </c>
-      <c r="J35" t="n">
-        <v>64</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-18.03041</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-70.27101</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>28 DE JULIO</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-18.01452</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-70.24681</v>
-      </c>
-      <c r="I36" t="n">
-        <v>681</v>
-      </c>
-      <c r="J36" t="n">
-        <v>42</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-18.01452</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-70.24681</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>681</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-18.00211</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-70.24512</v>
-      </c>
-      <c r="I37" t="n">
-        <v>1195</v>
-      </c>
-      <c r="J37" t="n">
-        <v>65</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-18.00211</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-70.24512</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1195</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>PARROQUIAL CORAZON DE MARIA</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-18.0214</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-70.23907</v>
-      </c>
-      <c r="I38" t="n">
-        <v>728</v>
-      </c>
-      <c r="J38" t="n">
-        <v>34</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-18.0214</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-70.23907</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>728</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>42006 SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-18.0059</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-70.25152</v>
-      </c>
-      <c r="I39" t="n">
-        <v>598</v>
-      </c>
-      <c r="J39" t="n">
-        <v>31</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-18.0059</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-70.25152</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>SAN JOSE FE Y ALEGRIA 40</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-18.0033</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-70.25711</v>
-      </c>
-      <c r="I40" t="n">
-        <v>920</v>
-      </c>
-      <c r="J40" t="n">
-        <v>48</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-18.0033</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-70.25711</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>920</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>CHAMPAGNAT</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-18.01496</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-70.24841000000001</v>
-      </c>
-      <c r="I41" t="n">
-        <v>961</v>
-      </c>
-      <c r="J41" t="n">
-        <v>55</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-18.01496</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-70.24841</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>ALEXANDER VON HUMBOLDT</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-18.02783</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-70.24797</v>
-      </c>
-      <c r="I42" t="n">
-        <v>861</v>
-      </c>
-      <c r="J42" t="n">
-        <v>43</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-18.02783</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-70.24797</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>861</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>SANTA MARIA</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-18.01682</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-70.25175</v>
-      </c>
-      <c r="I43" t="n">
-        <v>235</v>
-      </c>
-      <c r="J43" t="n">
-        <v>18</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-18.01682</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-70.25175</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>HERMANAS BARCIA BONIFFATTI</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-18.01193</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-70.23585</v>
-      </c>
-      <c r="I44" t="n">
-        <v>259</v>
-      </c>
-      <c r="J44" t="n">
-        <v>17</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-18.01193</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-70.23585</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>42218 MARISCAL CACERES</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-17.9852</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-70.24002</v>
-      </c>
-      <c r="I45" t="n">
-        <v>1371</v>
-      </c>
-      <c r="J45" t="n">
-        <v>77</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-17.9852</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-70.24002</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1371</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>42250 CESAR AUGUSTO COHAILA TAMAYO / 42250 CESAR COHAILA TAMAYO</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-17.97326</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-70.22995</v>
-      </c>
-      <c r="I46" t="n">
-        <v>858</v>
-      </c>
-      <c r="J46" t="n">
-        <v>76</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-17.97326</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-70.22995</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>858</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>42072 CAROLINA FREYRE ARIAS</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-17.862398</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-70.559517</v>
-      </c>
-      <c r="I47" t="n">
-        <v>313</v>
-      </c>
-      <c r="J47" t="n">
-        <v>18</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-17.862398</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-70.559517</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>PARADISE INTERNATIONAL COLLEGE</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-18.01998</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-70.25691999999999</v>
-      </c>
-      <c r="I48" t="n">
-        <v>357</v>
-      </c>
-      <c r="J48" t="n">
-        <v>32</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-18.01998</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-70.25692</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>PERUANO BRITANICO</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-18.02688</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-70.24751999999999</v>
-      </c>
-      <c r="I49" t="n">
-        <v>248</v>
-      </c>
-      <c r="J49" t="n">
-        <v>17</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-18.02688</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-70.24752</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>SAN PABLO</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-18.01353</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-70.24252</v>
-      </c>
-      <c r="I50" t="n">
-        <v>218</v>
-      </c>
-      <c r="J50" t="n">
-        <v>25</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-18.01353</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-70.24252</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>CIMA</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-18.0156</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-70.24222</v>
-      </c>
-      <c r="I51" t="n">
-        <v>929</v>
-      </c>
-      <c r="J51" t="n">
-        <v>54</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-18.0156</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-70.24222</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3121,20 +3609,30 @@
           <t>449 EDUARDO PEREZ GAMBOA</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-18.0683</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-70.29940000000001</v>
-      </c>
-      <c r="I52" t="n">
-        <v>264</v>
-      </c>
-      <c r="J52" t="n">
-        <v>15</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-18.0683</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-70.2994</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3173,20 +3671,30 @@
           <t>FEDERICO VILLARREAL</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>-18.00876</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-70.23635</v>
-      </c>
-      <c r="I53" t="n">
-        <v>533</v>
-      </c>
-      <c r="J53" t="n">
-        <v>34</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-18.00876</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-70.23635</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>533</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3225,20 +3733,30 @@
           <t>INNOVA SCHOOLS - TACNA CEDROS</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>-18.02537</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-70.25915999999999</v>
-      </c>
-      <c r="I54" t="n">
-        <v>1287</v>
-      </c>
-      <c r="J54" t="n">
-        <v>63</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-18.02537</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-70.25916</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1287</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3277,20 +3795,30 @@
           <t>ALEXANDER FLEMING</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>-18.0228</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-70.25277</v>
-      </c>
-      <c r="I55" t="n">
-        <v>264</v>
-      </c>
-      <c r="J55" t="n">
-        <v>26</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-18.0228</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-70.25277</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3329,20 +3857,30 @@
           <t>MARISTA DE TACNA</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>-18.00297</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-70.23455</v>
-      </c>
-      <c r="I56" t="n">
-        <v>263</v>
-      </c>
-      <c r="J56" t="n">
-        <v>21</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-18.00297</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-70.23455</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3381,20 +3919,30 @@
           <t>EL BUEN PASTOR</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>-18.00432</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-70.23788999999999</v>
-      </c>
-      <c r="I57" t="n">
-        <v>202</v>
-      </c>
-      <c r="J57" t="n">
-        <v>22</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-18.00432</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-70.23789</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3433,20 +3981,30 @@
           <t>LA TORRE</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>-18.01338</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-70.24259000000001</v>
-      </c>
-      <c r="I58" t="n">
-        <v>261</v>
-      </c>
-      <c r="J58" t="n">
-        <v>19</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-18.01338</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-70.24259</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3485,20 +4043,30 @@
           <t>CUMBRES</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>-18.01936</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-70.22933</v>
-      </c>
-      <c r="I59" t="n">
-        <v>289</v>
-      </c>
-      <c r="J59" t="n">
-        <v>11</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-18.01936</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-70.22933</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3537,20 +4105,30 @@
           <t>STEVE JOBS COLLEGE</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>-18.01982</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-70.25221000000001</v>
-      </c>
-      <c r="I60" t="n">
-        <v>215</v>
-      </c>
-      <c r="J60" t="n">
-        <v>22</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-18.01982</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-70.25221</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3589,20 +4167,30 @@
           <t>INNOVA SCHOOLS - TACNA - POCOLLAY</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>-17.99414</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-70.22282</v>
-      </c>
-      <c r="I61" t="n">
-        <v>468</v>
-      </c>
-      <c r="J61" t="n">
-        <v>24</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-17.99414</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-70.22282</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/TACNA-TACNA-TACNA.xlsx
+++ b/ZonasEscolares/excels/TACNA-TACNA-TACNA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>57534</t>
+          <t>853216</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>INTERNACIONAL ELIM</t>
+          <t>CUMBRES</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-18.00742</t>
+          <t>-18.01936</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-70.24201</t>
+          <t>-70.22933</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>289</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>294583</t>
+          <t>486718</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>WILLIAM PRESCOTT</t>
+          <t>CORONEL BOLOGNESI</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-18.02175</t>
+          <t>-18.00538</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-70.26869</t>
+          <t>-70.25069</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>112</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>485931</t>
+          <t>486723</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>225 NIÑOS HEROES</t>
+          <t>FRANCISCO ANTONIO DE ZELA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-18.00218</t>
+          <t>-18.00527</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-70.23723</t>
+          <t>-70.23971</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>2267</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>136</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>486191</t>
+          <t>486412</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CLARITA GAMBETTA</t>
+          <t>42013 ROSA DOMINGA PEREZ LIENDO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-18.0292</t>
+          <t>-18.01292</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-70.26772</t>
+          <t>-70.2353</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>215</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>486228</t>
+          <t>486431</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>42217 NUESTROS HEROES DE LA GUERRA DEL PACIFICO</t>
+          <t>42015 ZOILA SABEL CACERES</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-18.0081</t>
+          <t>-18.00042</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-70.25818</t>
+          <t>-70.24842</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>248</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>486351</t>
+          <t>486191</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>42002 CARLOS WIESSE</t>
+          <t>CLARITA GAMBETTA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-18.01071</t>
+          <t>-18.0292</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-70.25084</t>
+          <t>-70.26772</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>220</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>486365</t>
+          <t>486469</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>42005 JOSE ROSA ARA</t>
+          <t>42020 ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-18.00307</t>
+          <t>-17.99802</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-70.23729</t>
+          <t>-70.23855</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>229</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>486370</t>
+          <t>486600</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>42007 LEONCIO PRADO</t>
+          <t>43007 LUIS BANCHERO ROSSI</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-18.00261</t>
+          <t>-17.99919</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-70.24893</t>
+          <t>-70.23435</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>270</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>486394</t>
+          <t>668501</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>42011 REPUBLICA ARGENTINA</t>
+          <t>449 EDUARDO PEREZ GAMBOA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-18.01512</t>
+          <t>-18.0683</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-70.25301</t>
+          <t>-70.2994</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>264</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>486412</t>
+          <t>485931</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>42013 ROSA DOMINGA PEREZ LIENDO</t>
+          <t>225 NIÑOS HEROES</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-18.01292</t>
+          <t>-18.00218</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-70.2353</t>
+          <t>-70.23723</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>328</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>486426</t>
+          <t>486596</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>42014 JOSE JIMENEZ BORJA</t>
+          <t>43005 MODESTO MOLINA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-18.00299</t>
+          <t>-18.01515</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-70.24482</t>
+          <t>-70.23356</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>225</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>486431</t>
+          <t>486445</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>42015 ZOILA SABEL CACERES</t>
+          <t>42016 MAXIMILIANA VELASQUEZ DE SOTILLO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-18.00042</t>
+          <t>-18.00464</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-70.24842</t>
+          <t>-70.25445</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>309</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,27 +1245,27 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>486445</t>
+          <t>487218</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>42016 MAXIMILIANA VELASQUEZ DE SOTILLO</t>
+          <t>HERMANAS BARCIA BONIFFATTI</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-18.00464</t>
+          <t>-18.01193</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-70.25445</t>
+          <t>-70.23585</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>259</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>486469</t>
+          <t>530146</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>42020 ALMIRANTE MIGUEL GRAU</t>
+          <t>PERUANO BRITANICO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-17.99802</t>
+          <t>-18.02688</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-70.23855</t>
+          <t>-70.24752</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>248</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>486474</t>
+          <t>486426</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>42022 DR. MODESTO MONTESINOS ZAMALLOA</t>
+          <t>42014 JOSE JIMENEZ BORJA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-18.01956</t>
+          <t>-18.00299</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-70.23916</t>
+          <t>-70.24482</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>412</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>486501</t>
+          <t>487176</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>COLEGIO DE ALTO RENDIMIENTO DE TACNA</t>
+          <t>SANTA MARIA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-18.049298</t>
+          <t>-18.01682</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-70.283728</t>
+          <t>-70.25175</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>235</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>486558</t>
+          <t>488487</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>42241 HERMOGENES ARENAS YAÑEZ</t>
+          <t>42072 CAROLINA FREYRE ARIAS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-18.03821</t>
+          <t>-17.862398</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-70.28108</t>
+          <t>-70.559517</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>313</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>486563</t>
+          <t>294583</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MIGUEL PRO</t>
+          <t>WILLIAM PRESCOTT</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-18.0678</t>
+          <t>-18.02175</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-70.29363</t>
+          <t>-70.26869</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>501</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>486582</t>
+          <t>851811</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>43001 HERMANOS BARRETO</t>
+          <t>LA TORRE</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-18.00799</t>
+          <t>-18.01338</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-70.24263</t>
+          <t>-70.24259</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>261</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>486596</t>
+          <t>57534</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>43005 MODESTO MOLINA</t>
+          <t>INTERNACIONAL ELIM</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-18.01515</t>
+          <t>-18.00742</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-70.23356</t>
+          <t>-70.24201</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>209</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>486600</t>
+          <t>486351</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>43007 LUIS BANCHERO ROSSI</t>
+          <t>42002 CARLOS WIESSE</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-17.99919</t>
+          <t>-18.01071</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-70.23435</t>
+          <t>-70.25084</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>474</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>486619</t>
+          <t>486474</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>43008 JORGE MARTORELL FLORES</t>
+          <t>42022 DR. MODESTO MONTESINOS ZAMALLOA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-18.01189</t>
+          <t>-18.01956</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-70.24473</t>
+          <t>-70.23916</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>273</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>486624</t>
+          <t>808752</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>43009 MARIA UGARTECHE DE MACLEAN</t>
+          <t>MARISTA DE TACNA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-18.00898</t>
+          <t>-18.00297</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-70.2451</t>
+          <t>-70.23455</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1170</t>
+          <t>263</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>486638</t>
+          <t>831173</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>42019 LASTENIA REJAS DE CASTAÑON</t>
+          <t>EL BUEN PASTOR</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-18.02572</t>
+          <t>-18.00432</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-70.26607</t>
+          <t>-70.23789</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>202</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>486643</t>
+          <t>853221</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>42003 CORONEL GREGORIO ALBARRACIN</t>
+          <t>STEVE JOBS COLLEGE</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-18.01802</t>
+          <t>-18.01982</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-70.25331</t>
+          <t>-70.25221</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>215</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>486657</t>
+          <t>486394</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>42010 SANTISIMA NIÑA MARIA</t>
+          <t>42011 REPUBLICA ARGENTINA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-18.00584</t>
+          <t>-18.01512</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-70.23817</t>
+          <t>-70.25301</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>504</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>486676</t>
+          <t>854918</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>42195 WILMA SOTILLO DE BACIGALUPO</t>
+          <t>INNOVA SCHOOLS - TACNA - POCOLLAY</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-18.03162</t>
+          <t>-17.99414</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-70.2752</t>
+          <t>-70.22282</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>468</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>486695</t>
+          <t>534535</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>43003 CARLOS ARMANDO LAURA</t>
+          <t>SAN PABLO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-18.00307</t>
+          <t>-18.01353</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-70.24244</t>
+          <t>-70.24252</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>218</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>486704</t>
+          <t>486370</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>43006 MERCEDES INDACOCHEA</t>
+          <t>42007 LEONCIO PRADO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-18.01151</t>
+          <t>-18.00261</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-70.25207</t>
+          <t>-70.24893</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>536</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>486718</t>
+          <t>486582</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CORONEL BOLOGNESI</t>
+          <t>43001 HERMANOS BARRETO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-18.00538</t>
+          <t>-18.00799</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-70.25069</t>
+          <t>-70.24263</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>558</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>486723</t>
+          <t>781031</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FRANCISCO ANTONIO DE ZELA</t>
+          <t>ALEXANDER FLEMING</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-18.00527</t>
+          <t>-18.0228</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-70.23971</t>
+          <t>-70.25277</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2267</t>
+          <t>264</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>486742</t>
+          <t>486563</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MODESTO BASADRE</t>
+          <t>MIGUEL PRO</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-18.00513</t>
+          <t>-18.0678</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-70.25674</t>
+          <t>-70.29363</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>438</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>486841</t>
+          <t>487082</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SANTA ANA</t>
+          <t>42006 SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-18.01889</t>
+          <t>-18.0059</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-70.24963</t>
+          <t>-70.25152</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>598</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,37 +2547,37 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>487015</t>
+          <t>530132</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CRISTO REY</t>
+          <t>PARADISE INTERNATIONAL COLLEGE</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-18.03041</t>
+          <t>-18.01998</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-70.27101</t>
+          <t>-70.25692</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>357</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>487044</t>
+          <t>486676</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>28 DE JULIO</t>
+          <t>42195 WILMA SOTILLO DE BACIGALUPO</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-18.01452</t>
+          <t>-18.03162</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-70.24681</t>
+          <t>-70.2752</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>678</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>487063</t>
+          <t>487077</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SAN MARTIN DE PORRES</t>
+          <t>PARROQUIAL CORAZON DE MARIA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-18.00211</t>
+          <t>-18.0214</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-70.24512</t>
+          <t>-70.23907</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>728</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,27 +2733,27 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>487077</t>
+          <t>715833</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PARROQUIAL CORAZON DE MARIA</t>
+          <t>FEDERICO VILLARREAL</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-18.0214</t>
+          <t>-18.00876</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-70.23907</t>
+          <t>-70.23635</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>533</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>487082</t>
+          <t>486365</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>42006 SAN FRANCISCO DE ASIS</t>
+          <t>42005 JOSE ROSA ARA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-18.0059</t>
+          <t>-18.00307</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-70.25152</t>
+          <t>-70.23729</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>665</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>487096</t>
+          <t>486501</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SAN JOSE FE Y ALEGRIA 40</t>
+          <t>COLEGIO DE ALTO RENDIMIENTO DE TACNA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-18.0033</t>
+          <t>-18.049298</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-70.25711</t>
+          <t>-70.283728</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>294</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>487100</t>
+          <t>486558</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CHAMPAGNAT</t>
+          <t>42241 HERMOGENES ARENAS YAÑEZ</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-18.01496</t>
+          <t>-18.03821</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-70.24841</t>
+          <t>-70.28108</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>611</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>487119</t>
+          <t>487044</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ALEXANDER VON HUMBOLDT</t>
+          <t>28 DE JULIO</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-18.02783</t>
+          <t>-18.01452</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-70.24797</t>
+          <t>-70.24681</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>681</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>487176</t>
+          <t>487119</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SANTA MARIA</t>
+          <t>ALEXANDER VON HUMBOLDT</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-18.01682</t>
+          <t>-18.02783</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-70.25175</t>
+          <t>-70.24797</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>861</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>487218</t>
+          <t>486228</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>HERMANAS BARCIA BONIFFATTI</t>
+          <t>42217 NUESTROS HEROES DE LA GUERRA DEL PACIFICO</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-18.01193</t>
+          <t>-18.0081</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-70.23585</t>
+          <t>-70.25818</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>994</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>487826</t>
+          <t>486695</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>42218 MARISCAL CACERES</t>
+          <t>43003 CARLOS ARMANDO LAURA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-17.9852</t>
+          <t>-18.00307</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-70.24002</t>
+          <t>-70.24244</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>855</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>487845</t>
+          <t>487096</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>42250 CESAR AUGUSTO COHAILA TAMAYO / 42250 CESAR COHAILA TAMAYO</t>
+          <t>SAN JOSE FE Y ALEGRIA 40</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-17.97326</t>
+          <t>-18.0033</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-70.22995</t>
+          <t>-70.25711</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>920</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>488487</t>
+          <t>486704</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>42072 CAROLINA FREYRE ARIAS</t>
+          <t>43006 MERCEDES INDACOCHEA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-17.862398</t>
+          <t>-18.01151</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-70.559517</t>
+          <t>-70.25207</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>788</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>530132</t>
+          <t>589504</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>PARADISE INTERNATIONAL COLLEGE</t>
+          <t>CIMA</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-18.01998</t>
+          <t>-18.0156</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-70.25692</t>
+          <t>-70.24222</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>929</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>530146</t>
+          <t>487100</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>PERUANO BRITANICO</t>
+          <t>CHAMPAGNAT</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-18.02688</t>
+          <t>-18.01496</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-70.24752</t>
+          <t>-70.24841</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>961</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>534535</t>
+          <t>486638</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SAN PABLO</t>
+          <t>42019 LASTENIA REJAS DE CASTAÑON</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-18.01353</t>
+          <t>-18.02572</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-70.24252</t>
+          <t>-70.26607</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>589504</t>
+          <t>486657</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CIMA</t>
+          <t>42010 SANTISIMA NIÑA MARIA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-18.0156</t>
+          <t>-18.00584</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-70.24222</t>
+          <t>-70.23817</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>903</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>668501</t>
+          <t>486619</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>449 EDUARDO PEREZ GAMBOA</t>
+          <t>43008 JORGE MARTORELL FLORES</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-18.0683</t>
+          <t>-18.01189</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-70.2994</t>
+          <t>-70.24473</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>715833</t>
+          <t>486624</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FEDERICO VILLARREAL</t>
+          <t>43009 MARIA UGARTECHE DE MACLEAN</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-18.00876</t>
+          <t>-18.00898</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-70.23635</t>
+          <t>-70.2451</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>1170</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3787,37 +3787,37 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>781031</t>
+          <t>487015</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ALEXANDER FLEMING</t>
+          <t>CRISTO REY</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-18.0228</t>
+          <t>-18.03041</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-70.25277</t>
+          <t>-70.27101</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>961</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>808752</t>
+          <t>487063</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MARISTA DE TACNA</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-18.00297</t>
+          <t>-18.00211</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-70.23455</t>
+          <t>-70.24512</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>831173</t>
+          <t>486643</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>EL BUEN PASTOR</t>
+          <t>42003 CORONEL GREGORIO ALBARRACIN</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-18.00432</t>
+          <t>-18.01802</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-70.23789</t>
+          <t>-70.25331</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>66</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>851811</t>
+          <t>486841</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>LA TORRE</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-18.01338</t>
+          <t>-18.01889</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-70.24259</t>
+          <t>-70.24963</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>610</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>72</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>853216</t>
+          <t>486742</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CUMBRES</t>
+          <t>MODESTO BASADRE</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-18.01936</t>
+          <t>-18.00513</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-70.22933</t>
+          <t>-70.25674</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>905</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>76</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>853221</t>
+          <t>487845</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>STEVE JOBS COLLEGE</t>
+          <t>42250 CESAR AUGUSTO COHAILA TAMAYO / 42250 CESAR COHAILA TAMAYO</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-18.01982</t>
+          <t>-17.97326</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-70.25221</t>
+          <t>-70.22995</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>858</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>76</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>854918</t>
+          <t>487826</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - TACNA - POCOLLAY</t>
+          <t>42218 MARISCAL CACERES</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-17.99414</t>
+          <t>-17.9852</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-70.22282</t>
+          <t>-70.24002</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>77</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">

--- a/ZonasEscolares/excels/TACNA-TACNA-TACNA.xlsx
+++ b/ZonasEscolares/excels/TACNA-TACNA-TACNA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>853216</t>
+          <t>854918</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CUMBRES</t>
+          <t>INNOVA SCHOOLS - TACNA - POCOLLAY</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-18.01936</t>
+          <t>468</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-70.22933</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>-17.99414</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-70.22282</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>486718</t>
+          <t>853221</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CORONEL BOLOGNESI</t>
+          <t>STEVE JOBS COLLEGE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-18.00538</t>
+          <t>215</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-70.25069</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>-18.01982</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>-70.25221</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>486723</t>
+          <t>853216</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FRANCISCO ANTONIO DE ZELA</t>
+          <t>CUMBRES</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-18.00527</t>
+          <t>289</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-70.23971</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2267</t>
+          <t>-18.01936</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>-70.22933</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>486412</t>
+          <t>851811</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>42013 ROSA DOMINGA PEREZ LIENDO</t>
+          <t>LA TORRE</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-18.01292</t>
+          <t>261</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-70.2353</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>-18.01338</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-70.24259</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>486431</t>
+          <t>831173</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>42015 ZOILA SABEL CACERES</t>
+          <t>EL BUEN PASTOR</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-18.00042</t>
+          <t>202</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-70.24842</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>-18.00432</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-70.23789</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>486191</t>
+          <t>808752</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CLARITA GAMBETTA</t>
+          <t>MARISTA DE TACNA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-18.0292</t>
+          <t>263</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-70.26772</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>-18.00297</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-70.23455</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>486469</t>
+          <t>781031</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>42020 ALMIRANTE MIGUEL GRAU</t>
+          <t>ALEXANDER FLEMING</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-17.99802</t>
+          <t>264</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-70.23855</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>-18.0228</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-70.25277</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>486600</t>
+          <t>781026</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>43007 LUIS BANCHERO ROSSI</t>
+          <t>INNOVA SCHOOLS - TACNA CEDROS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-17.99919</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-70.23435</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>-18.02537</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-70.25916</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>668501</t>
+          <t>715833</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>449 EDUARDO PEREZ GAMBOA</t>
+          <t>FEDERICO VILLARREAL</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-18.0683</t>
+          <t>533</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-70.2994</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>-18.00876</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-70.23635</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>485931</t>
+          <t>668501</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>225 NIÑOS HEROES</t>
+          <t>449 EDUARDO PEREZ GAMBOA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-18.00218</t>
+          <t>264</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-70.23723</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>-18.0683</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-70.2994</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>486596</t>
+          <t>589504</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>43005 MODESTO MOLINA</t>
+          <t>CIMA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-18.01515</t>
+          <t>929</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-70.23356</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>-18.0156</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-70.24222</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>486445</t>
+          <t>534535</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>42016 MAXIMILIANA VELASQUEZ DE SOTILLO</t>
+          <t>SAN PABLO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-18.00464</t>
+          <t>218</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-70.25445</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>-18.01353</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-70.24252</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>487218</t>
+          <t>530146</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>HERMANAS BARCIA BONIFFATTI</t>
+          <t>PERUANO BRITANICO</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-18.01193</t>
+          <t>248</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-70.23585</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>-18.02688</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-70.24752</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>530146</t>
+          <t>530132</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PERUANO BRITANICO</t>
+          <t>PARADISE INTERNATIONAL COLLEGE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-18.02688</t>
+          <t>357</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-70.24752</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>-18.01998</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-70.25692</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>486426</t>
+          <t>488487</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>42014 JOSE JIMENEZ BORJA</t>
+          <t>42072 CAROLINA FREYRE ARIAS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-18.00299</t>
+          <t>313</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-70.24482</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>-17.862398</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-70.559517</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>487176</t>
+          <t>487845</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SANTA MARIA</t>
+          <t>42250 CESAR AUGUSTO COHAILA TAMAYO / 42250 CESAR COHAILA TAMAYO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-18.01682</t>
+          <t>858</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-70.25175</t>
+          <t>76</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>-17.97326</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-70.22995</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>488487</t>
+          <t>487826</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>42072 CAROLINA FREYRE ARIAS</t>
+          <t>42218 MARISCAL CACERES</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-17.862398</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-70.559517</t>
+          <t>77</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>-17.9852</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-70.24002</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>294583</t>
+          <t>487218</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>WILLIAM PRESCOTT</t>
+          <t>HERMANAS BARCIA BONIFFATTI</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-18.02175</t>
+          <t>259</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-70.26869</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>-18.01193</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-70.23585</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>851811</t>
+          <t>487176</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>LA TORRE</t>
+          <t>SANTA MARIA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-18.01338</t>
+          <t>235</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-70.24259</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>-18.01682</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-70.25175</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>57534</t>
+          <t>487119</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>INTERNACIONAL ELIM</t>
+          <t>ALEXANDER VON HUMBOLDT</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-18.00742</t>
+          <t>861</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-70.24201</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>-18.02783</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-70.24797</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>486351</t>
+          <t>487100</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>42002 CARLOS WIESSE</t>
+          <t>CHAMPAGNAT</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-18.01071</t>
+          <t>961</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-70.25084</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>-18.01496</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-70.24841</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>486474</t>
+          <t>487096</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>42022 DR. MODESTO MONTESINOS ZAMALLOA</t>
+          <t>SAN JOSE FE Y ALEGRIA 40</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-18.01956</t>
+          <t>920</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-70.23916</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>-18.0033</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-70.25711</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>808752</t>
+          <t>487082</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MARISTA DE TACNA</t>
+          <t>42006 SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-18.00297</t>
+          <t>598</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-70.23455</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>-18.0059</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-70.25152</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>831173</t>
+          <t>487077</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>EL BUEN PASTOR</t>
+          <t>PARROQUIAL CORAZON DE MARIA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-18.00432</t>
+          <t>728</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-70.23789</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>-18.0214</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-70.23907</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>853221</t>
+          <t>487063</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>STEVE JOBS COLLEGE</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-18.01982</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-70.25221</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>-18.00211</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-70.24512</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>486394</t>
+          <t>487044</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>42011 REPUBLICA ARGENTINA</t>
+          <t>28 DE JULIO</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-18.01512</t>
+          <t>681</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-70.25301</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>-18.01452</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-70.24681</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,37 +2113,37 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>854918</t>
+          <t>487015</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - TACNA - POCOLLAY</t>
+          <t>CRISTO REY</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-17.99414</t>
+          <t>961</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-70.22282</t>
+          <t>64</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>-18.03041</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-70.27101</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>534535</t>
+          <t>486841</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SAN PABLO</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-18.01353</t>
+          <t>610</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-70.24252</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>-18.01889</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-70.24963</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>486370</t>
+          <t>486742</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>42007 LEONCIO PRADO</t>
+          <t>MODESTO BASADRE</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-18.00261</t>
+          <t>905</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-70.24893</t>
+          <t>76</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>-18.00513</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-70.25674</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>486582</t>
+          <t>486723</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>43001 HERMANOS BARRETO</t>
+          <t>FRANCISCO ANTONIO DE ZELA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-18.00799</t>
+          <t>2267</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-70.24263</t>
+          <t>136</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>-18.00527</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-70.23971</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>781031</t>
+          <t>486718</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ALEXANDER FLEMING</t>
+          <t>CORONEL BOLOGNESI</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-18.0228</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-70.25277</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>-18.00538</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-70.25069</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>486563</t>
+          <t>486704</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MIGUEL PRO</t>
+          <t>43006 MERCEDES INDACOCHEA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-18.0678</t>
+          <t>788</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-70.29363</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>-18.01151</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-70.25207</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>487082</t>
+          <t>486695</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>42006 SAN FRANCISCO DE ASIS</t>
+          <t>43003 CARLOS ARMANDO LAURA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-18.0059</t>
+          <t>855</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-70.25152</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>-18.00307</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-70.24244</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>530132</t>
+          <t>486676</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PARADISE INTERNATIONAL COLLEGE</t>
+          <t>42195 WILMA SOTILLO DE BACIGALUPO</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-18.01998</t>
+          <t>678</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-70.25692</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>-18.03162</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-70.2752</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>486676</t>
+          <t>486657</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>42195 WILMA SOTILLO DE BACIGALUPO</t>
+          <t>42010 SANTISIMA NIÑA MARIA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-18.03162</t>
+          <t>903</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-70.2752</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>-18.00584</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-70.23817</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>487077</t>
+          <t>486643</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PARROQUIAL CORAZON DE MARIA</t>
+          <t>42003 CORONEL GREGORIO ALBARRACIN</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-18.0214</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-70.23907</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>-18.01802</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-70.25331</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>715833</t>
+          <t>486638</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FEDERICO VILLARREAL</t>
+          <t>42019 LASTENIA REJAS DE CASTAÑON</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-18.00876</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-70.23635</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>-18.02572</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-70.26607</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>486365</t>
+          <t>486624</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>42005 JOSE ROSA ARA</t>
+          <t>43009 MARIA UGARTECHE DE MACLEAN</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-18.00307</t>
+          <t>1170</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-70.23729</t>
+          <t>62</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>-18.00898</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-70.2451</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>486501</t>
+          <t>486619</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>COLEGIO DE ALTO RENDIMIENTO DE TACNA</t>
+          <t>43008 JORGE MARTORELL FLORES</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-18.049298</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-70.283728</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>-18.01189</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-70.24473</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>486558</t>
+          <t>486600</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>42241 HERMOGENES ARENAS YAÑEZ</t>
+          <t>43007 LUIS BANCHERO ROSSI</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-18.03821</t>
+          <t>270</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-70.28108</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>-17.99919</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-70.23435</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>487044</t>
+          <t>486596</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>28 DE JULIO</t>
+          <t>43005 MODESTO MOLINA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-18.01452</t>
+          <t>225</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-70.24681</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>-18.01515</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-70.23356</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>487119</t>
+          <t>486582</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>ALEXANDER VON HUMBOLDT</t>
+          <t>43001 HERMANOS BARRETO</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-18.02783</t>
+          <t>558</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-70.24797</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>-18.00799</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-70.24263</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>486228</t>
+          <t>486563</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>42217 NUESTROS HEROES DE LA GUERRA DEL PACIFICO</t>
+          <t>MIGUEL PRO</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-18.0081</t>
+          <t>438</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-70.25818</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>-18.0678</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-70.29363</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>486695</t>
+          <t>486558</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>43003 CARLOS ARMANDO LAURA</t>
+          <t>42241 HERMOGENES ARENAS YAÑEZ</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-18.00307</t>
+          <t>611</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-70.24244</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>-18.03821</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-70.28108</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>487096</t>
+          <t>486501</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SAN JOSE FE Y ALEGRIA 40</t>
+          <t>COLEGIO DE ALTO RENDIMIENTO DE TACNA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-18.0033</t>
+          <t>294</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-70.25711</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>-18.049298</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-70.283728</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>486704</t>
+          <t>486474</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>43006 MERCEDES INDACOCHEA</t>
+          <t>42022 DR. MODESTO MONTESINOS ZAMALLOA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-18.01151</t>
+          <t>273</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-70.25207</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>-18.01956</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-70.23916</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>589504</t>
+          <t>486469</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CIMA</t>
+          <t>42020 ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-18.0156</t>
+          <t>229</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-70.24222</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>-17.99802</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>-70.23855</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>487100</t>
+          <t>486445</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CHAMPAGNAT</t>
+          <t>42016 MAXIMILIANA VELASQUEZ DE SOTILLO</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-18.01496</t>
+          <t>309</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-70.24841</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>-18.00464</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>-70.25445</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>486638</t>
+          <t>486431</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>42019 LASTENIA REJAS DE CASTAÑON</t>
+          <t>42015 ZOILA SABEL CACERES</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-18.02572</t>
+          <t>248</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-70.26607</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>-18.00042</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>-70.24842</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>486657</t>
+          <t>486426</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>42010 SANTISIMA NIÑA MARIA</t>
+          <t>42014 JOSE JIMENEZ BORJA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-18.00584</t>
+          <t>412</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-70.23817</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>-18.00299</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>-70.24482</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>486619</t>
+          <t>486412</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>43008 JORGE MARTORELL FLORES</t>
+          <t>42013 ROSA DOMINGA PEREZ LIENDO</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-18.01189</t>
+          <t>215</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-70.24473</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>-18.01292</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>-70.2353</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>486624</t>
+          <t>486394</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>43009 MARIA UGARTECHE DE MACLEAN</t>
+          <t>42011 REPUBLICA ARGENTINA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-18.00898</t>
+          <t>504</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-70.2451</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1170</t>
+          <t>-18.01512</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>-70.25301</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>781026</t>
+          <t>486370</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - TACNA CEDROS</t>
+          <t>42007 LEONCIO PRADO</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-18.02537</t>
+          <t>536</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-70.25916</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>-18.00261</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-70.24893</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3787,37 +3787,37 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>487015</t>
+          <t>486365</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CRISTO REY</t>
+          <t>42005 JOSE ROSA ARA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-18.03041</t>
+          <t>665</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-70.27101</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>-18.00307</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>-70.23729</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>487063</t>
+          <t>486351</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SAN MARTIN DE PORRES</t>
+          <t>42002 CARLOS WIESSE</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-18.00211</t>
+          <t>474</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-70.24512</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>-18.01071</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>-70.25084</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>486643</t>
+          <t>486228</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>42003 CORONEL GREGORIO ALBARRACIN</t>
+          <t>42217 NUESTROS HEROES DE LA GUERRA DEL PACIFICO</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-18.01802</t>
+          <t>994</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-70.25331</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>-18.0081</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>-70.25818</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>486841</t>
+          <t>486191</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SANTA ANA</t>
+          <t>CLARITA GAMBETTA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-18.01889</t>
+          <t>220</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-70.24963</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>-18.0292</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>-70.26772</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>486742</t>
+          <t>485931</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MODESTO BASADRE</t>
+          <t>225 NIÑOS HEROES</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-18.00513</t>
+          <t>328</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-70.25674</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>-18.00218</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>-70.23723</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>487845</t>
+          <t>294583</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>42250 CESAR AUGUSTO COHAILA TAMAYO / 42250 CESAR COHAILA TAMAYO</t>
+          <t>WILLIAM PRESCOTT</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-17.97326</t>
+          <t>501</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-70.22995</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>-18.02175</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>-70.26869</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>487826</t>
+          <t>057534</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>42218 MARISCAL CACERES</t>
+          <t>INTERNACIONAL ELIM</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-17.9852</t>
+          <t>209</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-70.24002</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>-18.00742</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>-70.24201</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">

--- a/ZonasEscolares/excels/TACNA-TACNA-TACNA.xlsx
+++ b/ZonasEscolares/excels/TACNA-TACNA-TACNA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
